--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\OneDrive\Desktop\py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A890E7-3B7E-4CA8-AC8B-D7E6A80BA842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4C08B7-AA7C-4487-A3C2-BCEA2C55A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,16 +333,16 @@
     <t>الرياضة البدنية 2</t>
   </si>
   <si>
-    <t xml:space="preserve"> معدل امتحان الاول </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> معدل امتحان الاخير</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> معدل امتحان الثاني</t>
-  </si>
-  <si>
     <t>االرياضة البدنية 3</t>
+  </si>
+  <si>
+    <t>معدل الامتحان الأول</t>
+  </si>
+  <si>
+    <t>معدل الامتحان الثاني</t>
+  </si>
+  <si>
+    <t>معدل الامتحان الأخير</t>
   </si>
 </sst>
 </file>
@@ -907,19 +907,19 @@
         <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>101</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>2</v>
@@ -1008,11 +1008,11 @@
         <v>9</v>
       </c>
       <c r="Y2" s="5">
-        <f>SUM(P2:X2)</f>
+        <f t="shared" ref="Y2:Y8" si="2">SUM(P2:X2)</f>
         <v>127</v>
       </c>
       <c r="Z2" s="10">
-        <f>AVERAGE(Y2/10)</f>
+        <f t="shared" ref="Z2:Z8" si="3">AVERAGE(Y2/10)</f>
         <v>12.7</v>
       </c>
       <c r="AA2" s="7">
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="AB2" s="8" t="str">
-        <f>IF(Z2&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" ref="AB2:AB11" si="4">IF(Z2&gt;=8,"ناجح","راسب")</f>
         <v>ناجح</v>
       </c>
       <c r="AC2" s="3">
@@ -1064,7 +1064,7 @@
         <v>12.7</v>
       </c>
       <c r="AP2" s="3">
-        <f t="shared" ref="AP2:AP60" si="2">AVERAGE(AM2:AO2)</f>
+        <f t="shared" ref="AP2:AP60" si="5">AVERAGE(AM2:AO2)</f>
         <v>10.699999999999998</v>
       </c>
       <c r="AQ2" s="1">
@@ -1118,7 +1118,7 @@
         <v>6.5</v>
       </c>
       <c r="N3" s="7">
-        <f t="shared" ref="N3:N8" si="3">RANK(L3,$L$2:$L$64)</f>
+        <f t="shared" ref="N3:N8" si="6">RANK(L3,$L$2:$L$64)</f>
         <v>38</v>
       </c>
       <c r="O3" s="8" t="str">
@@ -1153,11 +1153,11 @@
         <v>9</v>
       </c>
       <c r="Y3" s="5">
-        <f>SUM(P3:X3)</f>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="Z3" s="10">
-        <f>AVERAGE(Y3/10)</f>
+        <f t="shared" si="3"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="AA3" s="7">
@@ -1165,7 +1165,7 @@
         <v>29</v>
       </c>
       <c r="AB3" s="8" t="str">
-        <f>IF(Z3&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC3" s="3">
@@ -1196,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="AL3" s="3">
-        <f t="shared" ref="AL2:AL60" si="4">SUM(AC3:AK3)</f>
+        <f t="shared" ref="AL3:AL60" si="7">SUM(AC3:AK3)</f>
         <v>59</v>
       </c>
       <c r="AM3" s="3">
@@ -1209,11 +1209,11 @@
         <v>5.9</v>
       </c>
       <c r="AP3" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.2</v>
       </c>
       <c r="AQ3" s="1">
-        <f t="shared" ref="AQ3:AQ60" si="5">RANK(AP3,$AP$2:$AP$68)</f>
+        <f t="shared" ref="AQ3:AQ60" si="8">RANK(AP3,$AP$2:$AP$68)</f>
         <v>36</v>
       </c>
       <c r="AR3" s="1" t="str">
@@ -1263,7 +1263,7 @@
         <v>6.2</v>
       </c>
       <c r="N4" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="O4" s="8" t="str">
@@ -1298,19 +1298,19 @@
         <v>9</v>
       </c>
       <c r="Y4" s="5">
-        <f>SUM(P4:X4)</f>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="Z4" s="10">
-        <f>AVERAGE(Y4/10)</f>
+        <f t="shared" si="3"/>
         <v>6.8</v>
       </c>
       <c r="AA4" s="7">
-        <f t="shared" ref="AA4:AA8" si="6">RANK(Z4,$Z$2:$Z$59)</f>
+        <f t="shared" ref="AA4:AA8" si="9">RANK(Z4,$Z$2:$Z$59)</f>
         <v>48</v>
       </c>
       <c r="AB4" s="8" t="str">
-        <f>IF(Z4&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>راسب</v>
       </c>
       <c r="AC4" s="3">
@@ -1341,7 +1341,7 @@
         <v>9</v>
       </c>
       <c r="AL4" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>71</v>
       </c>
       <c r="AM4" s="3">
@@ -1354,11 +1354,11 @@
         <v>7.1</v>
       </c>
       <c r="AP4" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.7</v>
       </c>
       <c r="AQ4" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="AR4" s="1" t="str">
@@ -1408,7 +1408,7 @@
         <v>7.3</v>
       </c>
       <c r="N5" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="O5" s="8" t="str">
@@ -1443,19 +1443,19 @@
         <v>9</v>
       </c>
       <c r="Y5" s="5">
-        <f>SUM(P5:X5)</f>
+        <f t="shared" si="2"/>
         <v>112</v>
       </c>
       <c r="Z5" s="10">
-        <f>AVERAGE(Y5/10)</f>
+        <f t="shared" si="3"/>
         <v>11.2</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="AB5" s="8" t="str">
-        <f>IF(Z5&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC5" s="3">
@@ -1486,7 +1486,7 @@
         <v>9</v>
       </c>
       <c r="AL5" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>98.5</v>
       </c>
       <c r="AM5" s="3">
@@ -1499,11 +1499,11 @@
         <v>9.85</v>
       </c>
       <c r="AP5" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9.4500000000000011</v>
       </c>
       <c r="AQ5" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="AR5" s="1" t="str">
@@ -1553,7 +1553,7 @@
         <v>15.3</v>
       </c>
       <c r="N6" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="O6" s="8" t="str">
@@ -1588,19 +1588,19 @@
         <v>9</v>
       </c>
       <c r="Y6" s="5">
-        <f>SUM(P6:X6)</f>
+        <f t="shared" si="2"/>
         <v>169</v>
       </c>
       <c r="Z6" s="10">
-        <f>AVERAGE(Y6/10)</f>
+        <f t="shared" si="3"/>
         <v>16.899999999999999</v>
       </c>
       <c r="AA6" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="AB6" s="8" t="str">
-        <f>IF(Z6&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC6" s="3">
@@ -1631,7 +1631,7 @@
         <v>9</v>
       </c>
       <c r="AL6" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>156</v>
       </c>
       <c r="AM6" s="3">
@@ -1644,11 +1644,11 @@
         <v>15.6</v>
       </c>
       <c r="AP6" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15.933333333333335</v>
       </c>
       <c r="AQ6" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="AR6" s="1" t="str">
@@ -1698,7 +1698,7 @@
         <v>10.55</v>
       </c>
       <c r="N7" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="O7" s="8" t="str">
@@ -1733,19 +1733,19 @@
         <v>9</v>
       </c>
       <c r="Y7" s="5">
-        <f>SUM(P7:X7)</f>
+        <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="Z7" s="10">
-        <f>AVERAGE(Y7/10)</f>
+        <f t="shared" si="3"/>
         <v>11.6</v>
       </c>
       <c r="AA7" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="AB7" s="8" t="str">
-        <f>IF(Z7&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC7" s="3">
@@ -1776,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="AL7" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>111</v>
       </c>
       <c r="AM7" s="3">
@@ -1789,11 +1789,11 @@
         <v>11.1</v>
       </c>
       <c r="AP7" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.083333333333334</v>
       </c>
       <c r="AQ7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="AR7" s="1" t="str">
@@ -1843,7 +1843,7 @@
         <v>11.95</v>
       </c>
       <c r="N8" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="O8" s="8" t="str">
@@ -1878,19 +1878,19 @@
         <v>9</v>
       </c>
       <c r="Y8" s="5">
-        <f>SUM(P8:X8)</f>
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="Z8" s="10">
-        <f>AVERAGE(Y8/10)</f>
+        <f t="shared" si="3"/>
         <v>15.6</v>
       </c>
       <c r="AA8" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="AB8" s="8" t="str">
-        <f>IF(Z8&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC8" s="3">
@@ -1921,7 +1921,7 @@
         <v>9</v>
       </c>
       <c r="AL8" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>122</v>
       </c>
       <c r="AM8" s="3">
@@ -1934,11 +1934,11 @@
         <v>12.2</v>
       </c>
       <c r="AP8" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13.25</v>
       </c>
       <c r="AQ8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="AR8" s="1" t="str">
@@ -1988,7 +1988,7 @@
         <v>#N/A</v>
       </c>
       <c r="AB9" s="8" t="str">
-        <f>IF(Z9&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>راسب</v>
       </c>
       <c r="AC9" s="3"/>
@@ -2001,7 +2001,7 @@
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM9" s="3"/>
@@ -2012,11 +2012,11 @@
         <v>0</v>
       </c>
       <c r="AP9" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AQ9" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>59</v>
       </c>
       <c r="AR9" s="1" t="str">
@@ -2059,14 +2059,14 @@
         <v>8</v>
       </c>
       <c r="L10" s="5">
-        <f t="shared" ref="L10:L60" si="7">SUM(C10:K10)</f>
+        <f t="shared" ref="L10:L60" si="10">SUM(C10:K10)</f>
         <v>78</v>
       </c>
       <c r="M10" s="9">
         <v>7.8</v>
       </c>
       <c r="N10" s="7">
-        <f t="shared" ref="N10:N60" si="8">RANK(L10,$L$2:$L$64)</f>
+        <f t="shared" ref="N10:N60" si="11">RANK(L10,$L$2:$L$64)</f>
         <v>22</v>
       </c>
       <c r="O10" s="8" t="str">
@@ -2101,19 +2101,19 @@
         <v>9</v>
       </c>
       <c r="Y10" s="5">
-        <f>SUM(P10:X10)</f>
+        <f t="shared" ref="Y10:Y52" si="12">SUM(P10:X10)</f>
         <v>112</v>
       </c>
       <c r="Z10" s="10">
-        <f>AVERAGE(Y10/10)</f>
+        <f t="shared" ref="Z10:Z52" si="13">AVERAGE(Y10/10)</f>
         <v>11.2</v>
       </c>
       <c r="AA10" s="7">
-        <f t="shared" ref="AA10:AA59" si="9">RANK(Z10,$Z$2:$Z$59)</f>
+        <f t="shared" ref="AA10:AA59" si="14">RANK(Z10,$Z$2:$Z$59)</f>
         <v>23</v>
       </c>
       <c r="AB10" s="8" t="str">
-        <f>IF(Z10&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC10" s="3">
@@ -2144,7 +2144,7 @@
         <v>9</v>
       </c>
       <c r="AL10" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>88</v>
       </c>
       <c r="AM10" s="3">
@@ -2157,11 +2157,11 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="AP10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9.2666666666666675</v>
       </c>
       <c r="AQ10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="AR10" s="1" t="str">
@@ -2204,14 +2204,14 @@
         <v>7</v>
       </c>
       <c r="L11" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>60.5</v>
       </c>
       <c r="M11" s="9">
         <v>6.05</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="O11" s="8" t="str">
@@ -2246,19 +2246,19 @@
         <v>9</v>
       </c>
       <c r="Y11" s="5">
-        <f>SUM(P11:X11)</f>
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="Z11" s="10">
-        <f>AVERAGE(Y11/10)</f>
+        <f t="shared" si="13"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="AB11" s="8" t="str">
-        <f>IF(Z11&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="4"/>
         <v>ناجح</v>
       </c>
       <c r="AC11" s="3">
@@ -2289,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="AL11" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="AM11" s="3">
@@ -2302,11 +2302,11 @@
         <v>7.5</v>
       </c>
       <c r="AP11" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.583333333333333</v>
       </c>
       <c r="AQ11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="AR11" s="1" t="str">
@@ -2349,14 +2349,14 @@
         <v>10</v>
       </c>
       <c r="L12" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>166.5</v>
       </c>
       <c r="M12" s="9">
         <v>16.649999999999999</v>
       </c>
       <c r="N12" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="O12" s="8" t="str">
@@ -2391,15 +2391,15 @@
         <v>9</v>
       </c>
       <c r="Y12" s="5">
-        <f>SUM(P12:X12)</f>
+        <f t="shared" si="12"/>
         <v>171</v>
       </c>
       <c r="Z12" s="10">
-        <f>AVERAGE(Y12/10)</f>
+        <f t="shared" si="13"/>
         <v>17.100000000000001</v>
       </c>
       <c r="AA12" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AB12" s="8" t="str">
@@ -2434,7 +2434,7 @@
         <v>9</v>
       </c>
       <c r="AL12" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>155</v>
       </c>
       <c r="AM12" s="3">
@@ -2447,11 +2447,11 @@
         <v>15.5</v>
       </c>
       <c r="AP12" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16.416666666666668</v>
       </c>
       <c r="AQ12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="AR12" s="1" t="str">
@@ -2494,14 +2494,14 @@
         <v>9</v>
       </c>
       <c r="L13" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>106</v>
       </c>
       <c r="M13" s="9">
         <v>10.6</v>
       </c>
       <c r="N13" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="O13" s="8" t="str">
@@ -2536,19 +2536,19 @@
         <v>9</v>
       </c>
       <c r="Y13" s="5">
-        <f>SUM(P13:X13)</f>
+        <f t="shared" si="12"/>
         <v>119</v>
       </c>
       <c r="Z13" s="10">
-        <f>AVERAGE(Y13/10)</f>
+        <f t="shared" si="13"/>
         <v>11.9</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>19</v>
       </c>
       <c r="AB13" s="8" t="str">
-        <f>IF(Z13&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" ref="AB13:AB59" si="15">IF(Z13&gt;=8,"ناجح","راسب")</f>
         <v>ناجح</v>
       </c>
       <c r="AC13" s="3">
@@ -2579,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="AL13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>113</v>
       </c>
       <c r="AM13" s="3">
@@ -2592,11 +2592,11 @@
         <v>11.3</v>
       </c>
       <c r="AP13" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.266666666666666</v>
       </c>
       <c r="AQ13" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="AR13" s="1" t="str">
@@ -2629,14 +2629,14 @@
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>17</v>
       </c>
       <c r="M14" s="9">
         <v>1.7</v>
       </c>
       <c r="N14" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>55</v>
       </c>
       <c r="O14" s="8" t="str">
@@ -2671,19 +2671,19 @@
         <v>9</v>
       </c>
       <c r="Y14" s="5">
-        <f>SUM(P14:X14)</f>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="Z14" s="10">
-        <f>AVERAGE(Y14/10)</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="AA14" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>44</v>
       </c>
       <c r="AB14" s="8" t="str">
-        <f>IF(Z14&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC14" s="3"/>
@@ -2696,7 +2696,7 @@
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM14" s="3">
@@ -2709,11 +2709,11 @@
         <v>0</v>
       </c>
       <c r="AP14" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.9</v>
       </c>
       <c r="AQ14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>54</v>
       </c>
       <c r="AR14" s="1" t="str">
@@ -2740,14 +2740,14 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M15" s="9">
         <v>0</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>56</v>
       </c>
       <c r="O15" s="8" t="str">
@@ -2782,19 +2782,19 @@
         <v>9</v>
       </c>
       <c r="Y15" s="5">
-        <f>SUM(P15:X15)</f>
+        <f t="shared" si="12"/>
         <v>55</v>
       </c>
       <c r="Z15" s="10">
-        <f>AVERAGE(Y15/10)</f>
+        <f t="shared" si="13"/>
         <v>5.5</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>51</v>
       </c>
       <c r="AB15" s="8" t="str">
-        <f>IF(Z15&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC15" s="3">
@@ -2825,7 +2825,7 @@
         <v>9</v>
       </c>
       <c r="AL15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="AM15" s="3">
@@ -2838,11 +2838,11 @@
         <v>6.8</v>
       </c>
       <c r="AP15" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.1000000000000005</v>
       </c>
       <c r="AQ15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>52</v>
       </c>
       <c r="AR15" s="1" t="str">
@@ -2885,14 +2885,14 @@
         <v>7</v>
       </c>
       <c r="L16" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>64</v>
       </c>
       <c r="M16" s="9">
         <v>6.4</v>
       </c>
       <c r="N16" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>39</v>
       </c>
       <c r="O16" s="8" t="str">
@@ -2927,19 +2927,19 @@
         <v>9</v>
       </c>
       <c r="Y16" s="5">
-        <f>SUM(P16:X16)</f>
+        <f t="shared" si="12"/>
         <v>82</v>
       </c>
       <c r="Z16" s="10">
-        <f>AVERAGE(Y16/10)</f>
+        <f t="shared" si="13"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="AA16" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>35</v>
       </c>
       <c r="AB16" s="8" t="str">
-        <f>IF(Z16&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC16" s="3">
@@ -2970,7 +2970,7 @@
         <v>9</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>72</v>
       </c>
       <c r="AM16" s="3">
@@ -2983,11 +2983,11 @@
         <v>7.2</v>
       </c>
       <c r="AP16" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.2666666666666666</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="AR16" s="1" t="str">
@@ -3026,14 +3026,14 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>23</v>
       </c>
       <c r="M17" s="9">
         <v>2.2999999999999998</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>54</v>
       </c>
       <c r="O17" s="8" t="str">
@@ -3052,19 +3052,19 @@
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5">
-        <f>SUM(P17:X17)</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="Z17" s="10">
-        <f>AVERAGE(Y17/10)</f>
+        <f t="shared" si="13"/>
         <v>1.5</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>55</v>
       </c>
       <c r="AB17" s="8" t="str">
-        <f>IF(Z17&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC17" s="3"/>
@@ -3077,7 +3077,7 @@
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM17" s="3">
@@ -3090,11 +3090,11 @@
         <v>0</v>
       </c>
       <c r="AP17" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.2666666666666666</v>
       </c>
       <c r="AQ17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>58</v>
       </c>
       <c r="AR17" s="1" t="str">
@@ -3137,14 +3137,14 @@
         <v>10</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>105</v>
       </c>
       <c r="M18" s="9">
         <v>10.5</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="O18" s="8" t="str">
@@ -3179,19 +3179,19 @@
         <v>9</v>
       </c>
       <c r="Y18" s="5">
-        <f>SUM(P18:X18)</f>
+        <f t="shared" si="12"/>
         <v>106</v>
       </c>
       <c r="Z18" s="10">
-        <f>AVERAGE(Y18/10)</f>
+        <f t="shared" si="13"/>
         <v>10.6</v>
       </c>
       <c r="AA18" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>27</v>
       </c>
       <c r="AB18" s="8" t="str">
-        <f>IF(Z18&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC18" s="3"/>
@@ -3204,7 +3204,7 @@
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM18" s="3">
@@ -3217,11 +3217,11 @@
         <v>0</v>
       </c>
       <c r="AP18" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.0333333333333341</v>
       </c>
       <c r="AQ18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="AR18" s="1" t="str">
@@ -3264,14 +3264,14 @@
         <v>8</v>
       </c>
       <c r="L19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>78</v>
       </c>
       <c r="M19" s="9">
         <v>7.8</v>
       </c>
       <c r="N19" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="O19" s="8" t="str">
@@ -3306,19 +3306,19 @@
         <v>9</v>
       </c>
       <c r="Y19" s="5">
-        <f>SUM(P19:X19)</f>
+        <f t="shared" si="12"/>
         <v>134</v>
       </c>
       <c r="Z19" s="10">
-        <f>AVERAGE(Y19/10)</f>
+        <f t="shared" si="13"/>
         <v>13.4</v>
       </c>
       <c r="AA19" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>9</v>
       </c>
       <c r="AB19" s="8" t="str">
-        <f>IF(Z19&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC19" s="3">
@@ -3349,7 +3349,7 @@
         <v>9</v>
       </c>
       <c r="AL19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="AM19" s="3">
@@ -3362,11 +3362,11 @@
         <v>11</v>
       </c>
       <c r="AP19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10.733333333333334</v>
       </c>
       <c r="AQ19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="AR19" s="1" t="str">
@@ -3409,14 +3409,14 @@
         <v>8</v>
       </c>
       <c r="L20" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>121.5</v>
       </c>
       <c r="M20" s="9">
         <v>12.15</v>
       </c>
       <c r="N20" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="O20" s="8" t="str">
@@ -3451,19 +3451,19 @@
         <v>9</v>
       </c>
       <c r="Y20" s="5">
-        <f>SUM(P20:X20)</f>
+        <f t="shared" si="12"/>
         <v>131</v>
       </c>
       <c r="Z20" s="10">
-        <f>AVERAGE(Y20/10)</f>
+        <f t="shared" si="13"/>
         <v>13.1</v>
       </c>
       <c r="AA20" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>13</v>
       </c>
       <c r="AB20" s="8" t="str">
-        <f>IF(Z20&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC20" s="3">
@@ -3494,7 +3494,7 @@
         <v>9</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>128</v>
       </c>
       <c r="AM20" s="3">
@@ -3507,11 +3507,11 @@
         <v>12.8</v>
       </c>
       <c r="AP20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>12.683333333333332</v>
       </c>
       <c r="AQ20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="AR20" s="1" t="str">
@@ -3554,14 +3554,14 @@
         <v>9</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="M21" s="9">
         <v>9</v>
       </c>
       <c r="N21" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="O21" s="8" t="str">
@@ -3596,19 +3596,19 @@
         <v>9</v>
       </c>
       <c r="Y21" s="5">
-        <f>SUM(P21:X21)</f>
+        <f t="shared" si="12"/>
         <v>122</v>
       </c>
       <c r="Z21" s="10">
-        <f>AVERAGE(Y21/10)</f>
+        <f t="shared" si="13"/>
         <v>12.2</v>
       </c>
       <c r="AA21" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>18</v>
       </c>
       <c r="AB21" s="8" t="str">
-        <f>IF(Z21&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC21" s="3">
@@ -3637,7 +3637,7 @@
         <v>9</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>113.5</v>
       </c>
       <c r="AM21" s="3">
@@ -3650,11 +3650,11 @@
         <v>11.35</v>
       </c>
       <c r="AP21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10.85</v>
       </c>
       <c r="AQ21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="AR21" s="1" t="str">
@@ -3697,14 +3697,14 @@
         <v>7</v>
       </c>
       <c r="L22" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>94</v>
       </c>
       <c r="M22" s="9">
         <v>9.4</v>
       </c>
       <c r="N22" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="O22" s="8" t="str">
@@ -3739,19 +3739,19 @@
         <v>9</v>
       </c>
       <c r="Y22" s="5">
-        <f>SUM(P22:X22)</f>
+        <f t="shared" si="12"/>
         <v>150</v>
       </c>
       <c r="Z22" s="10">
-        <f>AVERAGE(Y22/10)</f>
+        <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="AA22" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>6</v>
       </c>
       <c r="AB22" s="8" t="str">
-        <f>IF(Z22&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC22" s="3">
@@ -3782,7 +3782,7 @@
         <v>9</v>
       </c>
       <c r="AL22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>152</v>
       </c>
       <c r="AM22" s="3">
@@ -3795,11 +3795,11 @@
         <v>15.2</v>
       </c>
       <c r="AP22" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13.199999999999998</v>
       </c>
       <c r="AQ22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="AR22" s="1" t="str">
@@ -3842,14 +3842,14 @@
         <v>8</v>
       </c>
       <c r="L23" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>119</v>
       </c>
       <c r="M23" s="9">
         <v>11.9</v>
       </c>
       <c r="N23" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="O23" s="8" t="str">
@@ -3884,19 +3884,19 @@
         <v>9</v>
       </c>
       <c r="Y23" s="5">
-        <f>SUM(P23:X23)</f>
+        <f t="shared" si="12"/>
         <v>81</v>
       </c>
       <c r="Z23" s="10">
-        <f>AVERAGE(Y23/10)</f>
+        <f t="shared" si="13"/>
         <v>8.1</v>
       </c>
       <c r="AA23" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="AB23" s="8" t="str">
-        <f>IF(Z23&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC23" s="3">
@@ -3927,7 +3927,7 @@
         <v>9</v>
       </c>
       <c r="AL23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="AM23" s="3">
@@ -3940,11 +3940,11 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="AP23" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9.4333333333333336</v>
       </c>
       <c r="AQ23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="AR23" s="1" t="str">
@@ -3987,14 +3987,14 @@
         <v>9</v>
       </c>
       <c r="L24" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>71</v>
       </c>
       <c r="M24" s="9">
         <v>7.1</v>
       </c>
       <c r="N24" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="O24" s="8" t="str">
@@ -4029,19 +4029,19 @@
         <v>9</v>
       </c>
       <c r="Y24" s="5">
-        <f>SUM(P24:X24)</f>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="Z24" s="10">
-        <f>AVERAGE(Y24/10)</f>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="AA24" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="AB24" s="8" t="str">
-        <f>IF(Z24&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC24" s="3">
@@ -4072,7 +4072,7 @@
         <v>9</v>
       </c>
       <c r="AL24" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>85</v>
       </c>
       <c r="AM24" s="3">
@@ -4085,11 +4085,11 @@
         <v>8.5</v>
       </c>
       <c r="AP24" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8.5333333333333332</v>
       </c>
       <c r="AQ24" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>29</v>
       </c>
       <c r="AR24" s="1" t="str">
@@ -4130,14 +4130,14 @@
         <v>0</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32</v>
       </c>
       <c r="M25" s="9">
         <v>3.2</v>
       </c>
       <c r="N25" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>51</v>
       </c>
       <c r="O25" s="8" t="str">
@@ -4156,19 +4156,19 @@
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5">
-        <f>SUM(P25:X25)</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="Z25" s="10">
-        <f>AVERAGE(Y25/10)</f>
+        <f t="shared" si="13"/>
         <v>1.5</v>
       </c>
       <c r="AA25" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>55</v>
       </c>
       <c r="AB25" s="8" t="str">
-        <f>IF(Z25&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC25" s="3"/>
@@ -4181,7 +4181,7 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM25" s="3">
@@ -4194,11 +4194,11 @@
         <v>0</v>
       </c>
       <c r="AP25" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.5666666666666667</v>
       </c>
       <c r="AQ25" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>57</v>
       </c>
       <c r="AR25" s="1" t="str">
@@ -4241,14 +4241,14 @@
         <v>5</v>
       </c>
       <c r="L26" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>58.5</v>
       </c>
       <c r="M26" s="9">
         <v>5.85</v>
       </c>
       <c r="N26" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>46</v>
       </c>
       <c r="O26" s="8" t="str">
@@ -4283,19 +4283,19 @@
         <v>9</v>
       </c>
       <c r="Y26" s="5">
-        <f>SUM(P26:X26)</f>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="Z26" s="10">
-        <f>AVERAGE(Y26/10)</f>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="AA26" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>44</v>
       </c>
       <c r="AB26" s="8" t="str">
-        <f>IF(Z26&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC26" s="3">
@@ -4326,7 +4326,7 @@
         <v>9</v>
       </c>
       <c r="AL26" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="AM26" s="3">
@@ -4339,11 +4339,11 @@
         <v>5</v>
       </c>
       <c r="AP26" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.95</v>
       </c>
       <c r="AQ26" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>47</v>
       </c>
       <c r="AR26" s="1" t="str">
@@ -4384,14 +4384,14 @@
         <v>0</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>25</v>
       </c>
       <c r="M27" s="9">
         <v>2.5</v>
       </c>
       <c r="N27" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>53</v>
       </c>
       <c r="O27" s="8" t="str">
@@ -4418,19 +4418,19 @@
         <v>9</v>
       </c>
       <c r="Y27" s="5">
-        <f>SUM(P27:X27)</f>
+        <f t="shared" si="12"/>
         <v>74</v>
       </c>
       <c r="Z27" s="10">
-        <f>AVERAGE(Y27/10)</f>
+        <f t="shared" si="13"/>
         <v>7.4</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="AB27" s="8" t="str">
-        <f>IF(Z27&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC27" s="3">
@@ -4461,7 +4461,7 @@
         <v>9</v>
       </c>
       <c r="AL27" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>51</v>
       </c>
       <c r="AM27" s="3">
@@ -4474,11 +4474,11 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AP27" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="AQ27" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="AR27" s="1" t="str">
@@ -4521,14 +4521,14 @@
         <v>10</v>
       </c>
       <c r="L28" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>101</v>
       </c>
       <c r="M28" s="9">
         <v>10.1</v>
       </c>
       <c r="N28" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="O28" s="8" t="str">
@@ -4563,19 +4563,19 @@
         <v>9</v>
       </c>
       <c r="Y28" s="5">
-        <f>SUM(P28:X28)</f>
+        <f t="shared" si="12"/>
         <v>140</v>
       </c>
       <c r="Z28" s="10">
-        <f>AVERAGE(Y28/10)</f>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="AA28" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>8</v>
       </c>
       <c r="AB28" s="8" t="str">
-        <f>IF(Z28&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC28" s="3">
@@ -4606,7 +4606,7 @@
         <v>9</v>
       </c>
       <c r="AL28" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>131</v>
       </c>
       <c r="AM28" s="3">
@@ -4619,11 +4619,11 @@
         <v>13.1</v>
       </c>
       <c r="AP28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>12.4</v>
       </c>
       <c r="AQ28" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="AR28" s="1" t="str">
@@ -4666,14 +4666,14 @@
         <v>10</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>105.5</v>
       </c>
       <c r="M29" s="9">
         <v>10.55</v>
       </c>
       <c r="N29" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="O29" s="8" t="str">
@@ -4708,19 +4708,19 @@
         <v>9</v>
       </c>
       <c r="Y29" s="5">
-        <f>SUM(P29:X29)</f>
+        <f t="shared" si="12"/>
         <v>114</v>
       </c>
       <c r="Z29" s="10">
-        <f>AVERAGE(Y29/10)</f>
+        <f t="shared" si="13"/>
         <v>11.4</v>
       </c>
       <c r="AA29" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>22</v>
       </c>
       <c r="AB29" s="8" t="str">
-        <f>IF(Z29&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC29" s="3">
@@ -4751,7 +4751,7 @@
         <v>9</v>
       </c>
       <c r="AL29" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>116</v>
       </c>
       <c r="AM29" s="3">
@@ -4764,11 +4764,11 @@
         <v>11.6</v>
       </c>
       <c r="AP29" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.183333333333335</v>
       </c>
       <c r="AQ29" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="AR29" s="1" t="str">
@@ -4811,14 +4811,14 @@
         <v>10</v>
       </c>
       <c r="L30" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>165.5</v>
       </c>
       <c r="M30" s="9">
         <v>16.55</v>
       </c>
       <c r="N30" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="O30" s="8" t="str">
@@ -4853,19 +4853,19 @@
         <v>9</v>
       </c>
       <c r="Y30" s="5">
-        <f>SUM(P30:X30)</f>
+        <f t="shared" si="12"/>
         <v>167</v>
       </c>
       <c r="Z30" s="10">
-        <f>AVERAGE(Y30/10)</f>
+        <f t="shared" si="13"/>
         <v>16.7</v>
       </c>
       <c r="AA30" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="AB30" s="8" t="str">
-        <f>IF(Z30&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC30" s="3">
@@ -4896,7 +4896,7 @@
         <v>9</v>
       </c>
       <c r="AL30" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="AM30" s="3">
@@ -4909,11 +4909,11 @@
         <v>15</v>
       </c>
       <c r="AP30" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16.083333333333332</v>
       </c>
       <c r="AQ30" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="AR30" s="1" t="str">
@@ -4956,14 +4956,14 @@
         <v>7</v>
       </c>
       <c r="L31" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>119</v>
       </c>
       <c r="M31" s="9">
         <v>11.9</v>
       </c>
       <c r="N31" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="O31" s="8" t="str">
@@ -4998,19 +4998,19 @@
         <v>9</v>
       </c>
       <c r="Y31" s="5">
-        <f>SUM(P31:X31)</f>
+        <f t="shared" si="12"/>
         <v>128</v>
       </c>
       <c r="Z31" s="10">
-        <f>AVERAGE(Y31/10)</f>
+        <f t="shared" si="13"/>
         <v>12.8</v>
       </c>
       <c r="AA31" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="AB31" s="8" t="str">
-        <f>IF(Z31&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC31" s="3">
@@ -5041,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="AL31" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>96</v>
       </c>
       <c r="AM31" s="3">
@@ -5054,11 +5054,11 @@
         <v>9.6</v>
       </c>
       <c r="AP31" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.433333333333335</v>
       </c>
       <c r="AQ31" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="AR31" s="1" t="str">
@@ -5101,14 +5101,14 @@
         <v>7</v>
       </c>
       <c r="L32" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>76.5</v>
       </c>
       <c r="M32" s="9">
         <v>7.65</v>
       </c>
       <c r="N32" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
       <c r="O32" s="8" t="str">
@@ -5143,19 +5143,19 @@
         <v>9</v>
       </c>
       <c r="Y32" s="5">
-        <f>SUM(P32:X32)</f>
+        <f t="shared" si="12"/>
         <v>116</v>
       </c>
       <c r="Z32" s="10">
-        <f>AVERAGE(Y32/10)</f>
+        <f t="shared" si="13"/>
         <v>11.6</v>
       </c>
       <c r="AA32" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="AB32" s="8" t="str">
-        <f>IF(Z32&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC32" s="3">
@@ -5186,7 +5186,7 @@
         <v>9</v>
       </c>
       <c r="AL32" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>116</v>
       </c>
       <c r="AM32" s="3">
@@ -5199,11 +5199,11 @@
         <v>11.6</v>
       </c>
       <c r="AP32" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10.283333333333333</v>
       </c>
       <c r="AQ32" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="AR32" s="1" t="str">
@@ -5246,14 +5246,14 @@
         <v>9</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>70.5</v>
       </c>
       <c r="M33" s="9">
         <v>7.05</v>
       </c>
       <c r="N33" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>32</v>
       </c>
       <c r="O33" s="8" t="str">
@@ -5288,19 +5288,19 @@
         <v>9</v>
       </c>
       <c r="Y33" s="5">
-        <f>SUM(P33:X33)</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="Z33" s="10">
-        <f>AVERAGE(Y33/10)</f>
+        <f t="shared" si="13"/>
         <v>8.4</v>
       </c>
       <c r="AA33" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>34</v>
       </c>
       <c r="AB33" s="8" t="str">
-        <f>IF(Z33&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC33" s="3">
@@ -5331,7 +5331,7 @@
         <v>9</v>
       </c>
       <c r="AL33" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
       <c r="AM33" s="3">
@@ -5344,11 +5344,11 @@
         <v>6.5</v>
       </c>
       <c r="AP33" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.3166666666666664</v>
       </c>
       <c r="AQ33" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="AR33" s="1" t="str">
@@ -5391,14 +5391,14 @@
         <v>6</v>
       </c>
       <c r="L34" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>62</v>
       </c>
       <c r="M34" s="9">
         <v>6.2</v>
       </c>
       <c r="N34" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="O34" s="8" t="str">
@@ -5433,19 +5433,19 @@
         <v>9</v>
       </c>
       <c r="Y34" s="5">
-        <f>SUM(P34:X34)</f>
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
       <c r="Z34" s="10">
-        <f>AVERAGE(Y34/10)</f>
+        <f t="shared" si="13"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="AA34" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>29</v>
       </c>
       <c r="AB34" s="8" t="str">
-        <f>IF(Z34&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC34" s="3">
@@ -5476,7 +5476,7 @@
         <v>9</v>
       </c>
       <c r="AL34" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>54</v>
       </c>
       <c r="AM34" s="3">
@@ -5489,11 +5489,11 @@
         <v>5.4</v>
       </c>
       <c r="AP34" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.9333333333333327</v>
       </c>
       <c r="AQ34" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="AR34" s="1" t="str">
@@ -5536,14 +5536,14 @@
         <v>9</v>
       </c>
       <c r="L35" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>74</v>
       </c>
       <c r="M35" s="9">
         <v>7.4</v>
       </c>
       <c r="N35" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="O35" s="8" t="str">
@@ -5578,19 +5578,19 @@
         <v>9</v>
       </c>
       <c r="Y35" s="5">
-        <f>SUM(P35:X35)</f>
+        <f t="shared" si="12"/>
         <v>109</v>
       </c>
       <c r="Z35" s="10">
-        <f>AVERAGE(Y35/10)</f>
+        <f t="shared" si="13"/>
         <v>10.9</v>
       </c>
       <c r="AA35" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="AB35" s="8" t="str">
-        <f>IF(Z35&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC35" s="3">
@@ -5621,7 +5621,7 @@
         <v>9</v>
       </c>
       <c r="AL35" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>121</v>
       </c>
       <c r="AM35" s="3">
@@ -5634,11 +5634,11 @@
         <v>12.1</v>
       </c>
       <c r="AP35" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10.133333333333333</v>
       </c>
       <c r="AQ35" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="AR35" s="1" t="str">
@@ -5681,14 +5681,14 @@
         <v>10</v>
       </c>
       <c r="L36" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>77</v>
       </c>
       <c r="M36" s="9">
         <v>7.7</v>
       </c>
       <c r="N36" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="O36" s="8" t="str">
@@ -5723,19 +5723,19 @@
         <v>9</v>
       </c>
       <c r="Y36" s="5">
-        <f>SUM(P36:X36)</f>
+        <f t="shared" si="12"/>
         <v>108</v>
       </c>
       <c r="Z36" s="10">
-        <f>AVERAGE(Y36/10)</f>
+        <f t="shared" si="13"/>
         <v>10.8</v>
       </c>
       <c r="AA36" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>26</v>
       </c>
       <c r="AB36" s="8" t="str">
-        <f>IF(Z36&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC36" s="3">
@@ -5766,7 +5766,7 @@
         <v>9</v>
       </c>
       <c r="AL36" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>96</v>
       </c>
       <c r="AM36" s="3">
@@ -5779,11 +5779,11 @@
         <v>9.6</v>
       </c>
       <c r="AP36" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9.3666666666666671</v>
       </c>
       <c r="AQ36" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="AR36" s="1" t="str">
@@ -5826,14 +5826,14 @@
         <v>7</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>66</v>
       </c>
       <c r="M37" s="9">
         <v>6.6</v>
       </c>
       <c r="N37" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
       <c r="O37" s="8" t="str">
@@ -5868,19 +5868,19 @@
         <v>9</v>
       </c>
       <c r="Y37" s="5">
-        <f>SUM(P37:X37)</f>
+        <f t="shared" si="12"/>
         <v>90</v>
       </c>
       <c r="Z37" s="10">
-        <f>AVERAGE(Y37/10)</f>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="AA37" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>32</v>
       </c>
       <c r="AB37" s="8" t="str">
-        <f>IF(Z37&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC37" s="3">
@@ -5911,7 +5911,7 @@
         <v>9</v>
       </c>
       <c r="AL37" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>82</v>
       </c>
       <c r="AM37" s="3">
@@ -5924,11 +5924,11 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="AP37" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.9333333333333327</v>
       </c>
       <c r="AQ37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="AR37" s="1" t="str">
@@ -5971,14 +5971,14 @@
         <v>6</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="M38" s="9">
         <v>5.6</v>
       </c>
       <c r="N38" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>47</v>
       </c>
       <c r="O38" s="8" t="str">
@@ -6013,19 +6013,19 @@
         <v>9</v>
       </c>
       <c r="Y38" s="5">
-        <f>SUM(P38:X38)</f>
+        <f t="shared" si="12"/>
         <v>67</v>
       </c>
       <c r="Z38" s="10">
-        <f>AVERAGE(Y38/10)</f>
+        <f t="shared" si="13"/>
         <v>6.7</v>
       </c>
       <c r="AA38" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>49</v>
       </c>
       <c r="AB38" s="8" t="str">
-        <f>IF(Z38&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC38" s="3">
@@ -6056,7 +6056,7 @@
         <v>9</v>
       </c>
       <c r="AL38" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>65</v>
       </c>
       <c r="AM38" s="3">
@@ -6069,11 +6069,11 @@
         <v>6.5</v>
       </c>
       <c r="AP38" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.2666666666666666</v>
       </c>
       <c r="AQ38" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>44</v>
       </c>
       <c r="AR38" s="1" t="str">
@@ -6116,14 +6116,14 @@
         <v>9</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="M39" s="9">
         <v>3</v>
       </c>
       <c r="N39" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>52</v>
       </c>
       <c r="O39" s="8" t="str">
@@ -6152,19 +6152,19 @@
         <v>9</v>
       </c>
       <c r="Y39" s="5">
-        <f>SUM(P39:X39)</f>
+        <f t="shared" si="12"/>
         <v>55</v>
       </c>
       <c r="Z39" s="10">
-        <f>AVERAGE(Y39/10)</f>
+        <f t="shared" si="13"/>
         <v>5.5</v>
       </c>
       <c r="AA39" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>51</v>
       </c>
       <c r="AB39" s="8" t="str">
-        <f>IF(Z39&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC39" s="3"/>
@@ -6177,7 +6177,7 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM39" s="3">
@@ -6190,11 +6190,11 @@
         <v>0</v>
       </c>
       <c r="AP39" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.8333333333333335</v>
       </c>
       <c r="AQ39" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>55</v>
       </c>
       <c r="AR39" s="1" t="str">
@@ -6237,14 +6237,14 @@
         <v>7</v>
       </c>
       <c r="L40" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>88</v>
       </c>
       <c r="M40" s="9">
         <v>8.8000000000000007</v>
       </c>
       <c r="N40" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="O40" s="8" t="str">
@@ -6279,19 +6279,19 @@
         <v>9</v>
       </c>
       <c r="Y40" s="5">
-        <f>SUM(P40:X40)</f>
+        <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="Z40" s="10">
-        <f>AVERAGE(Y40/10)</f>
+        <f t="shared" si="13"/>
         <v>6.9</v>
       </c>
       <c r="AA40" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>46</v>
       </c>
       <c r="AB40" s="8" t="str">
-        <f>IF(Z40&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC40" s="3"/>
@@ -6308,7 +6308,7 @@
         <v>9</v>
       </c>
       <c r="AL40" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="AM40" s="3">
@@ -6321,11 +6321,11 @@
         <v>1.7</v>
       </c>
       <c r="AP40" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.8000000000000007</v>
       </c>
       <c r="AQ40" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>48</v>
       </c>
       <c r="AR40" s="1" t="str">
@@ -6368,14 +6368,14 @@
         <v>9</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>78.5</v>
       </c>
       <c r="M41" s="9">
         <v>7.85</v>
       </c>
       <c r="N41" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>21</v>
       </c>
       <c r="O41" s="8" t="str">
@@ -6410,19 +6410,19 @@
         <v>9</v>
       </c>
       <c r="Y41" s="5">
-        <f>SUM(P41:X41)</f>
+        <f t="shared" si="12"/>
         <v>133</v>
       </c>
       <c r="Z41" s="10">
-        <f>AVERAGE(Y41/10)</f>
+        <f t="shared" si="13"/>
         <v>13.3</v>
       </c>
       <c r="AA41" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>11</v>
       </c>
       <c r="AB41" s="8" t="str">
-        <f>IF(Z41&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC41" s="3">
@@ -6453,7 +6453,7 @@
         <v>9</v>
       </c>
       <c r="AL41" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>129</v>
       </c>
       <c r="AM41" s="3">
@@ -6466,11 +6466,11 @@
         <v>12.9</v>
       </c>
       <c r="AP41" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.35</v>
       </c>
       <c r="AQ41" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="AR41" s="1" t="str">
@@ -6513,14 +6513,14 @@
         <v>8</v>
       </c>
       <c r="L42" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>83</v>
       </c>
       <c r="M42" s="9">
         <v>8.3000000000000007</v>
       </c>
       <c r="N42" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="O42" s="8" t="str">
@@ -6555,19 +6555,19 @@
         <v>9</v>
       </c>
       <c r="Y42" s="5">
-        <f>SUM(P42:X42)</f>
+        <f t="shared" si="12"/>
         <v>130</v>
       </c>
       <c r="Z42" s="10">
-        <f>AVERAGE(Y42/10)</f>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
       <c r="AA42" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AB42" s="8" t="str">
-        <f>IF(Z42&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC42" s="3">
@@ -6598,7 +6598,7 @@
         <v>9</v>
       </c>
       <c r="AL42" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>130</v>
       </c>
       <c r="AM42" s="3">
@@ -6611,11 +6611,11 @@
         <v>13</v>
       </c>
       <c r="AP42" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.433333333333332</v>
       </c>
       <c r="AQ42" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="AR42" s="1" t="str">
@@ -6658,14 +6658,14 @@
         <v>9</v>
       </c>
       <c r="L43" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="M43" s="9">
         <v>6</v>
       </c>
       <c r="N43" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
       <c r="O43" s="8" t="str">
@@ -6700,19 +6700,19 @@
         <v>9</v>
       </c>
       <c r="Y43" s="5">
-        <f>SUM(P43:X43)</f>
+        <f t="shared" si="12"/>
         <v>71</v>
       </c>
       <c r="Z43" s="10">
-        <f>AVERAGE(Y43/10)</f>
+        <f t="shared" si="13"/>
         <v>7.1</v>
       </c>
       <c r="AA43" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>43</v>
       </c>
       <c r="AB43" s="8" t="str">
-        <f>IF(Z43&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC43" s="3">
@@ -6743,7 +6743,7 @@
         <v>9</v>
       </c>
       <c r="AL43" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>59</v>
       </c>
       <c r="AM43" s="3">
@@ -6756,11 +6756,11 @@
         <v>5.9</v>
       </c>
       <c r="AP43" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.333333333333333</v>
       </c>
       <c r="AQ43" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>43</v>
       </c>
       <c r="AR43" s="1" t="str">
@@ -6803,14 +6803,14 @@
         <v>8</v>
       </c>
       <c r="L44" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>72.5</v>
       </c>
       <c r="M44" s="9">
         <v>7.25</v>
       </c>
       <c r="N44" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>30</v>
       </c>
       <c r="O44" s="8" t="str">
@@ -6845,19 +6845,19 @@
         <v>9</v>
       </c>
       <c r="Y44" s="5">
-        <f>SUM(P44:X44)</f>
+        <f t="shared" si="12"/>
         <v>133</v>
       </c>
       <c r="Z44" s="10">
-        <f>AVERAGE(Y44/10)</f>
+        <f t="shared" si="13"/>
         <v>13.3</v>
       </c>
       <c r="AA44" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>11</v>
       </c>
       <c r="AB44" s="8" t="str">
-        <f>IF(Z44&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC44" s="3">
@@ -6888,7 +6888,7 @@
         <v>9</v>
       </c>
       <c r="AL44" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>117</v>
       </c>
       <c r="AM44" s="3">
@@ -6901,11 +6901,11 @@
         <v>11.7</v>
       </c>
       <c r="AP44" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>10.75</v>
       </c>
       <c r="AQ44" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="AR44" s="1" t="str">
@@ -6948,14 +6948,14 @@
         <v>9</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>104.5</v>
       </c>
       <c r="M45" s="9">
         <v>10.45</v>
       </c>
       <c r="N45" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="O45" s="8" t="str">
@@ -6990,19 +6990,19 @@
         <v>9</v>
       </c>
       <c r="Y45" s="5">
-        <f>SUM(P45:X45)</f>
+        <f t="shared" si="12"/>
         <v>134</v>
       </c>
       <c r="Z45" s="10">
-        <f>AVERAGE(Y45/10)</f>
+        <f t="shared" si="13"/>
         <v>13.4</v>
       </c>
       <c r="AA45" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>9</v>
       </c>
       <c r="AB45" s="8" t="str">
-        <f>IF(Z45&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC45" s="3">
@@ -7033,7 +7033,7 @@
         <v>9</v>
       </c>
       <c r="AL45" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>167</v>
       </c>
       <c r="AM45" s="3">
@@ -7046,11 +7046,11 @@
         <v>16.7</v>
       </c>
       <c r="AP45" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>13.516666666666666</v>
       </c>
       <c r="AQ45" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="AR45" s="1" t="str">
@@ -7093,14 +7093,14 @@
         <v>9</v>
       </c>
       <c r="L46" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>56</v>
       </c>
       <c r="M46" s="9">
         <v>5.6</v>
       </c>
       <c r="N46" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>47</v>
       </c>
       <c r="O46" s="8" t="str">
@@ -7135,19 +7135,19 @@
         <v>9</v>
       </c>
       <c r="Y46" s="5">
-        <f>SUM(P46:X46)</f>
+        <f t="shared" si="12"/>
         <v>76</v>
       </c>
       <c r="Z46" s="10">
-        <f>AVERAGE(Y46/10)</f>
+        <f t="shared" si="13"/>
         <v>7.6</v>
       </c>
       <c r="AA46" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>39</v>
       </c>
       <c r="AB46" s="8" t="str">
-        <f>IF(Z46&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC46" s="3">
@@ -7178,7 +7178,7 @@
         <v>9</v>
       </c>
       <c r="AL46" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="AM46" s="3">
@@ -7191,11 +7191,11 @@
         <v>6.3</v>
       </c>
       <c r="AP46" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.5</v>
       </c>
       <c r="AQ46" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>42</v>
       </c>
       <c r="AR46" s="1" t="str">
@@ -7234,14 +7234,14 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>34</v>
       </c>
       <c r="M47" s="9">
         <v>3.4</v>
       </c>
       <c r="N47" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>50</v>
       </c>
       <c r="O47" s="8" t="str">
@@ -7276,19 +7276,19 @@
         <v>9</v>
       </c>
       <c r="Y47" s="5">
-        <f>SUM(P47:X47)</f>
+        <f t="shared" si="12"/>
         <v>75</v>
       </c>
       <c r="Z47" s="10">
-        <f>AVERAGE(Y47/10)</f>
+        <f t="shared" si="13"/>
         <v>7.5</v>
       </c>
       <c r="AA47" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>40</v>
       </c>
       <c r="AB47" s="8" t="str">
-        <f>IF(Z47&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC47" s="3">
@@ -7319,7 +7319,7 @@
         <v>9</v>
       </c>
       <c r="AL47" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>74</v>
       </c>
       <c r="AM47" s="3">
@@ -7332,11 +7332,11 @@
         <v>7.4</v>
       </c>
       <c r="AP47" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.1000000000000005</v>
       </c>
       <c r="AQ47" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="AR47" s="1" t="str">
@@ -7379,14 +7379,14 @@
         <v>9</v>
       </c>
       <c r="L48" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>103.5</v>
       </c>
       <c r="M48" s="9">
         <v>10.35</v>
       </c>
       <c r="N48" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="O48" s="8" t="str">
@@ -7421,19 +7421,19 @@
         <v>9</v>
       </c>
       <c r="Y48" s="5">
-        <f>SUM(P48:X48)</f>
+        <f t="shared" si="12"/>
         <v>141</v>
       </c>
       <c r="Z48" s="10">
-        <f>AVERAGE(Y48/10)</f>
+        <f t="shared" si="13"/>
         <v>14.1</v>
       </c>
       <c r="AA48" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>7</v>
       </c>
       <c r="AB48" s="8" t="str">
-        <f>IF(Z48&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC48" s="3">
@@ -7464,7 +7464,7 @@
         <v>9</v>
       </c>
       <c r="AL48" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>117</v>
       </c>
       <c r="AM48" s="3">
@@ -7477,11 +7477,11 @@
         <v>11.7</v>
       </c>
       <c r="AP48" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>12.049999999999999</v>
       </c>
       <c r="AQ48" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="AR48" s="1" t="str">
@@ -7524,14 +7524,14 @@
         <v>6</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>39</v>
       </c>
       <c r="M49" s="9">
         <v>3.9</v>
       </c>
       <c r="N49" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>49</v>
       </c>
       <c r="O49" s="8" t="str">
@@ -7566,19 +7566,19 @@
         <v>9</v>
       </c>
       <c r="Y49" s="5">
-        <f>SUM(P49:X49)</f>
+        <f t="shared" si="12"/>
         <v>45</v>
       </c>
       <c r="Z49" s="10">
-        <f>AVERAGE(Y49/10)</f>
+        <f t="shared" si="13"/>
         <v>4.5</v>
       </c>
       <c r="AA49" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>53</v>
       </c>
       <c r="AB49" s="8" t="str">
-        <f>IF(Z49&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC49" s="3">
@@ -7609,7 +7609,7 @@
         <v>9</v>
       </c>
       <c r="AL49" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>48</v>
       </c>
       <c r="AM49" s="3">
@@ -7622,15 +7622,15 @@
         <v>4.8</v>
       </c>
       <c r="AP49" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.3999999999999995</v>
       </c>
       <c r="AQ49" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
       <c r="AR49" s="1" t="str">
-        <f t="shared" ref="AR49:AR54" si="10">IF(AP49&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" ref="AR49:AR54" si="16">IF(AP49&gt;=8,"ناجح","راسب")</f>
         <v>راسب</v>
       </c>
     </row>
@@ -7669,14 +7669,14 @@
         <v>7</v>
       </c>
       <c r="L50" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>66.5</v>
       </c>
       <c r="M50" s="9">
         <v>6.65</v>
       </c>
       <c r="N50" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>36</v>
       </c>
       <c r="O50" s="8" t="str">
@@ -7711,19 +7711,19 @@
         <v>9</v>
       </c>
       <c r="Y50" s="5">
-        <f>SUM(P50:X50)</f>
+        <f t="shared" si="12"/>
         <v>62</v>
       </c>
       <c r="Z50" s="10">
-        <f>AVERAGE(Y50/10)</f>
+        <f t="shared" si="13"/>
         <v>6.2</v>
       </c>
       <c r="AA50" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>50</v>
       </c>
       <c r="AB50" s="8" t="str">
-        <f>IF(Z50&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC50" s="3">
@@ -7754,7 +7754,7 @@
         <v>9</v>
       </c>
       <c r="AL50" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>52</v>
       </c>
       <c r="AM50" s="3">
@@ -7767,15 +7767,15 @@
         <v>5.2</v>
       </c>
       <c r="AP50" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.0166666666666666</v>
       </c>
       <c r="AQ50" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>46</v>
       </c>
       <c r="AR50" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>راسب</v>
       </c>
     </row>
@@ -7814,14 +7814,14 @@
         <v>7</v>
       </c>
       <c r="L51" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>68</v>
       </c>
       <c r="M51" s="9">
         <v>6.8</v>
       </c>
       <c r="N51" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="O51" s="8" t="str">
@@ -7856,19 +7856,19 @@
         <v>9</v>
       </c>
       <c r="Y51" s="5">
-        <f>SUM(P51:X51)</f>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="Z51" s="10">
-        <f>AVERAGE(Y51/10)</f>
+        <f t="shared" si="13"/>
         <v>7.8</v>
       </c>
       <c r="AA51" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="AB51" s="8" t="str">
-        <f>IF(Z51&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC51" s="3">
@@ -7899,7 +7899,7 @@
         <v>9</v>
       </c>
       <c r="AL51" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>55</v>
       </c>
       <c r="AM51" s="3">
@@ -7912,15 +7912,15 @@
         <v>5.5</v>
       </c>
       <c r="AP51" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.7</v>
       </c>
       <c r="AQ51" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="AR51" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>راسب</v>
       </c>
     </row>
@@ -7959,14 +7959,14 @@
         <v>8</v>
       </c>
       <c r="L52" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="M52" s="9">
         <v>6</v>
       </c>
       <c r="N52" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>44</v>
       </c>
       <c r="O52" s="8" t="str">
@@ -8001,19 +8001,19 @@
         <v>9</v>
       </c>
       <c r="Y52" s="5">
-        <f>SUM(P52:X52)</f>
+        <f t="shared" si="12"/>
         <v>86</v>
       </c>
       <c r="Z52" s="10">
-        <f>AVERAGE(Y52/10)</f>
+        <f t="shared" si="13"/>
         <v>8.6</v>
       </c>
       <c r="AA52" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>33</v>
       </c>
       <c r="AB52" s="8" t="str">
-        <f>IF(Z52&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC52" s="3">
@@ -8044,7 +8044,7 @@
         <v>9</v>
       </c>
       <c r="AL52" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>79</v>
       </c>
       <c r="AM52" s="3">
@@ -8057,15 +8057,15 @@
         <v>7.9</v>
       </c>
       <c r="AP52" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.5</v>
       </c>
       <c r="AQ52" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="AR52" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>راسب</v>
       </c>
     </row>
@@ -8104,14 +8104,14 @@
         <v>8</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>60.5</v>
       </c>
       <c r="M53" s="9">
         <v>6.05</v>
       </c>
       <c r="N53" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="O53" s="8" t="str">
@@ -8130,11 +8130,11 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="10"/>
       <c r="AA53" s="7" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>#N/A</v>
       </c>
       <c r="AB53" s="8" t="str">
-        <f>IF(Z53&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC53" s="3"/>
@@ -8147,7 +8147,7 @@
       <c r="AJ53" s="3"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM53" s="3">
@@ -8160,15 +8160,15 @@
         <v>0</v>
       </c>
       <c r="AP53" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.0166666666666666</v>
       </c>
       <c r="AQ53" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>56</v>
       </c>
       <c r="AR53" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>راسب</v>
       </c>
     </row>
@@ -8207,14 +8207,14 @@
         <v>8</v>
       </c>
       <c r="L54" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>69.5</v>
       </c>
       <c r="M54" s="9">
         <v>6.95</v>
       </c>
       <c r="N54" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>33</v>
       </c>
       <c r="O54" s="8" t="str">
@@ -8249,19 +8249,19 @@
         <v>9</v>
       </c>
       <c r="Y54" s="5">
-        <f>SUM(P54:X54)</f>
+        <f t="shared" ref="Y54:Y59" si="17">SUM(P54:X54)</f>
         <v>69</v>
       </c>
       <c r="Z54" s="10">
-        <f>AVERAGE(Y54/10)</f>
+        <f t="shared" ref="Z54:Z59" si="18">AVERAGE(Y54/10)</f>
         <v>6.9</v>
       </c>
       <c r="AA54" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>46</v>
       </c>
       <c r="AB54" s="8" t="str">
-        <f>IF(Z54&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC54" s="3">
@@ -8292,7 +8292,7 @@
         <v>9</v>
       </c>
       <c r="AL54" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>66</v>
       </c>
       <c r="AM54" s="3">
@@ -8305,15 +8305,15 @@
         <v>6.6</v>
       </c>
       <c r="AP54" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.8166666666666673</v>
       </c>
       <c r="AQ54" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>39</v>
       </c>
       <c r="AR54" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>راسب</v>
       </c>
     </row>
@@ -8352,14 +8352,14 @@
         <v>10</v>
       </c>
       <c r="L55" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>96</v>
       </c>
       <c r="M55" s="9">
         <v>9.6</v>
       </c>
       <c r="N55" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="O55" s="8" t="str">
@@ -8394,19 +8394,19 @@
         <v>9</v>
       </c>
       <c r="Y55" s="5">
-        <f>SUM(P55:X55)</f>
+        <f t="shared" si="17"/>
         <v>126</v>
       </c>
       <c r="Z55" s="10">
-        <f>AVERAGE(Y55/10)</f>
+        <f t="shared" si="18"/>
         <v>12.6</v>
       </c>
       <c r="AA55" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>17</v>
       </c>
       <c r="AB55" s="8" t="str">
-        <f>IF(Z55&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC55" s="3">
@@ -8437,7 +8437,7 @@
         <v>9</v>
       </c>
       <c r="AL55" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>127</v>
       </c>
       <c r="AM55" s="3">
@@ -8450,11 +8450,11 @@
         <v>12.7</v>
       </c>
       <c r="AP55" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>11.633333333333333</v>
       </c>
       <c r="AQ55" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="AR55" s="1" t="str">
@@ -8497,14 +8497,14 @@
         <v>9</v>
       </c>
       <c r="L56" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>77</v>
       </c>
       <c r="M56" s="9">
         <v>7.7</v>
       </c>
       <c r="N56" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
       <c r="O56" s="8" t="str">
@@ -8539,19 +8539,19 @@
         <v>9</v>
       </c>
       <c r="Y56" s="5">
-        <f>SUM(P56:X56)</f>
+        <f t="shared" si="17"/>
         <v>74</v>
       </c>
       <c r="Z56" s="10">
-        <f>AVERAGE(Y56/10)</f>
+        <f t="shared" si="18"/>
         <v>7.4</v>
       </c>
       <c r="AA56" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>41</v>
       </c>
       <c r="AB56" s="8" t="str">
-        <f>IF(Z56&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC56" s="3">
@@ -8582,7 +8582,7 @@
         <v>9</v>
       </c>
       <c r="AL56" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>88</v>
       </c>
       <c r="AM56" s="3">
@@ -8595,11 +8595,11 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="AP56" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.9666666666666677</v>
       </c>
       <c r="AQ56" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="AR56" s="1" t="str">
@@ -8624,14 +8624,14 @@
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M57" s="9">
         <v>0</v>
       </c>
       <c r="N57" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>56</v>
       </c>
       <c r="O57" s="8" t="str">
@@ -8666,19 +8666,19 @@
         <v>9</v>
       </c>
       <c r="Y57" s="5">
-        <f>SUM(P57:X57)</f>
+        <f t="shared" si="17"/>
         <v>169</v>
       </c>
       <c r="Z57" s="10">
-        <f>AVERAGE(Y57/10)</f>
+        <f t="shared" si="18"/>
         <v>16.899999999999999</v>
       </c>
       <c r="AA57" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="AB57" s="8" t="str">
-        <f>IF(Z57&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC57" s="3">
@@ -8709,7 +8709,7 @@
         <v>9</v>
       </c>
       <c r="AL57" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>164.5</v>
       </c>
       <c r="AM57" s="3">
@@ -8722,11 +8722,11 @@
         <v>16.45</v>
       </c>
       <c r="AP57" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15.85</v>
       </c>
       <c r="AQ57" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="AR57" s="1" t="str">
@@ -8769,14 +8769,14 @@
         <v>8</v>
       </c>
       <c r="L58" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>75</v>
       </c>
       <c r="M58" s="9">
         <v>7.5</v>
       </c>
       <c r="N58" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>27</v>
       </c>
       <c r="O58" s="8" t="str">
@@ -8811,19 +8811,19 @@
         <v>9</v>
       </c>
       <c r="Y58" s="5">
-        <f>SUM(P58:X58)</f>
+        <f t="shared" si="17"/>
         <v>81</v>
       </c>
       <c r="Z58" s="10">
-        <f>AVERAGE(Y58/10)</f>
+        <f t="shared" si="18"/>
         <v>8.1</v>
       </c>
       <c r="AA58" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="AB58" s="8" t="str">
-        <f>IF(Z58&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>ناجح</v>
       </c>
       <c r="AC58" s="3">
@@ -8854,7 +8854,7 @@
         <v>9</v>
       </c>
       <c r="AL58" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>77</v>
       </c>
       <c r="AM58" s="3">
@@ -8867,11 +8867,11 @@
         <v>7.7</v>
       </c>
       <c r="AP58" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.2666666666666666</v>
       </c>
       <c r="AQ58" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>49</v>
       </c>
       <c r="AR58" s="1" t="str">
@@ -8896,14 +8896,14 @@
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M59" s="9">
         <v>0</v>
       </c>
       <c r="N59" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>56</v>
       </c>
       <c r="O59" s="8" t="str">
@@ -8922,19 +8922,19 @@
       <c r="W59" s="5"/>
       <c r="X59" s="5"/>
       <c r="Y59" s="5">
-        <f>SUM(P59:X59)</f>
+        <f t="shared" si="17"/>
         <v>24</v>
       </c>
       <c r="Z59" s="10">
-        <f>AVERAGE(Y59/10)</f>
+        <f t="shared" si="18"/>
         <v>2.4</v>
       </c>
       <c r="AA59" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>54</v>
       </c>
       <c r="AB59" s="8" t="str">
-        <f>IF(Z59&gt;=8,"ناجح","راسب")</f>
+        <f t="shared" si="15"/>
         <v>راسب</v>
       </c>
       <c r="AC59" s="3"/>
@@ -8947,7 +8947,7 @@
       <c r="AJ59" s="3"/>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM59" s="3">
@@ -8960,11 +8960,11 @@
         <v>0</v>
       </c>
       <c r="AP59" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="AQ59" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>53</v>
       </c>
       <c r="AR59" s="1" t="str">
@@ -9007,14 +9007,14 @@
         <v>10</v>
       </c>
       <c r="L60" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>180.5</v>
       </c>
       <c r="M60" s="9">
         <v>18.05</v>
       </c>
       <c r="N60" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O60" s="8" t="str">
@@ -9049,7 +9049,7 @@
         <v>9</v>
       </c>
       <c r="AL60" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>175</v>
       </c>
       <c r="AM60" s="3">
@@ -9060,11 +9060,11 @@
         <v>17.5</v>
       </c>
       <c r="AP60" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17.774999999999999</v>
       </c>
       <c r="AQ60" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AR60" s="1" t="str">

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\OneDrive\Desktop\py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4C08B7-AA7C-4487-A3C2-BCEA2C55A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC19057-6EEB-46EE-A333-7245F3E8D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,12 +45,6 @@
     <t>المعدل العام</t>
   </si>
   <si>
-    <t>الرتبة</t>
-  </si>
-  <si>
-    <t>القرار</t>
-  </si>
-  <si>
     <t>شامخ ولد محمد الأمين</t>
   </si>
   <si>
@@ -343,6 +337,12 @@
   </si>
   <si>
     <t>معدل الامتحان الأخير</t>
+  </si>
+  <si>
+    <t>الرتبة العامة</t>
+  </si>
+  <si>
+    <t>القرار العام</t>
   </si>
 </sst>
 </file>
@@ -805,130 +805,130 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="X1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5">
         <v>11</v>
@@ -1081,7 +1081,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5">
         <v>10</v>
@@ -1226,7 +1226,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5">
         <v>13</v>
@@ -1371,7 +1371,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5">
         <v>11</v>
@@ -1516,7 +1516,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="5">
         <v>27</v>
@@ -1661,7 +1661,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5">
         <v>15.5</v>
@@ -1806,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="5">
         <v>20.5</v>
@@ -1951,7 +1951,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5">
         <v>14</v>
@@ -2174,7 +2174,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5">
         <v>9.5</v>
@@ -2319,7 +2319,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" s="5">
         <v>28</v>
@@ -2464,7 +2464,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5">
         <v>14</v>
@@ -2609,7 +2609,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
@@ -2855,7 +2855,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="5">
         <v>11</v>
@@ -3000,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -3107,7 +3107,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="5">
         <v>16</v>
@@ -3234,7 +3234,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="5">
         <v>14</v>
@@ -3379,7 +3379,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="5">
         <v>15</v>
@@ -3524,7 +3524,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="5">
         <v>13</v>
@@ -3667,7 +3667,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="5">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="5">
         <v>22.5</v>
@@ -3957,7 +3957,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="5">
         <v>8</v>
@@ -4102,7 +4102,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="5">
         <v>3</v>
@@ -4211,7 +4211,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="5">
         <v>8</v>
@@ -4356,7 +4356,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
@@ -4491,7 +4491,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="5">
         <v>13</v>
@@ -4636,7 +4636,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="5">
         <v>14.5</v>
@@ -4781,7 +4781,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" s="5">
         <v>20</v>
@@ -4926,7 +4926,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" s="5">
         <v>20</v>
@@ -5071,7 +5071,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C32" s="5">
         <v>13.5</v>
@@ -5216,7 +5216,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C33" s="5">
         <v>11.5</v>
@@ -5361,7 +5361,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" s="5">
         <v>11</v>
@@ -5506,7 +5506,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C35" s="5">
         <v>11</v>
@@ -5651,7 +5651,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" s="5">
         <v>13</v>
@@ -5796,7 +5796,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C37" s="5">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="5">
         <v>8</v>
@@ -6086,7 +6086,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C39" s="5">
         <v>4</v>
@@ -6207,7 +6207,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C40" s="5">
         <v>9</v>
@@ -6338,7 +6338,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" s="5">
         <v>11</v>
@@ -6483,7 +6483,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C42" s="5">
         <v>12.5</v>
@@ -6628,7 +6628,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C43" s="5">
         <v>9</v>
@@ -6773,7 +6773,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C44" s="5">
         <v>12</v>
@@ -6918,7 +6918,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C45" s="5">
         <v>20</v>
@@ -7063,7 +7063,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C46" s="5">
         <v>8</v>
@@ -7208,7 +7208,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C47" s="5">
         <v>3</v>
@@ -7349,7 +7349,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C48" s="5">
         <v>21.5</v>
@@ -7494,7 +7494,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C49" s="5">
         <v>7</v>
@@ -7639,7 +7639,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C50" s="5">
         <v>12.5</v>
@@ -7784,7 +7784,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C51" s="5">
         <v>12</v>
@@ -7929,7 +7929,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C52" s="5">
         <v>8</v>
@@ -8074,7 +8074,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C53" s="5">
         <v>8</v>
@@ -8177,7 +8177,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C54" s="5">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C55" s="5">
         <v>8</v>
@@ -8467,7 +8467,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C56" s="5">
         <v>9</v>
@@ -8612,7 +8612,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -8739,7 +8739,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C58" s="5">
         <v>10</v>
@@ -8884,7 +8884,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -8977,7 +8977,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5">
         <v>29</v>

--- a/results.xlsx
+++ b/results.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="105">
   <si>
     <t>الرقم</t>
   </si>
@@ -282,9 +284,6 @@
     <t>اللغة العربية 3</t>
   </si>
   <si>
-    <t>التربية الإسلامية 3</t>
-  </si>
-  <si>
     <t>الرياضيات 3</t>
   </si>
   <si>
@@ -327,9 +326,6 @@
     <t>الرياضة البدنية 2</t>
   </si>
   <si>
-    <t>االرياضة البدنية 3</t>
-  </si>
-  <si>
     <t>معدل الامتحان الأول</t>
   </si>
   <si>
@@ -343,6 +339,12 @@
   </si>
   <si>
     <t>القرار العام</t>
+  </si>
+  <si>
+    <t>الرياضة البدنية 3</t>
+  </si>
+  <si>
+    <t>التربية الاسلامية 3</t>
   </si>
 </sst>
 </file>
@@ -780,24 +782,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR61"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="16.09765625" customWidth="1"/>
-    <col min="3" max="3" width="17.09765625" customWidth="1"/>
-    <col min="4" max="4" width="13.8984375" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" customWidth="1"/>
-    <col min="6" max="6" width="14.69921875" customWidth="1"/>
-    <col min="7" max="7" width="17.69921875" customWidth="1"/>
-    <col min="8" max="8" width="12.19921875" customWidth="1"/>
-    <col min="27" max="27" width="14.19921875" customWidth="1"/>
-    <col min="29" max="29" width="13.59765625" customWidth="1"/>
-    <col min="30" max="30" width="12.8984375" customWidth="1"/>
-    <col min="39" max="39" width="11.5" customWidth="1"/>
-    <col min="40" max="40" width="9.69921875" customWidth="1"/>
-    <col min="41" max="41" width="12.19921875" customWidth="1"/>
+    <col min="2" max="2" width="16.05859375" customWidth="1"/>
+    <col min="3" max="3" width="17.0390625" customWidth="1"/>
+    <col min="4" max="4" width="13.8515625" customWidth="1"/>
+    <col min="5" max="5" width="12.37890625" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.65234375" customWidth="1"/>
+    <col min="8" max="8" width="12.13671875" customWidth="1"/>
+    <col min="27" max="27" width="14.21875" customWidth="1"/>
+    <col min="29" max="29" width="13.60546875" customWidth="1"/>
+    <col min="30" max="30" width="12.87109375" customWidth="1"/>
+    <col min="39" max="39" width="11.5234375" customWidth="1"/>
+    <col min="40" max="40" width="9.68359375" customWidth="1"/>
+    <col min="41" max="41" width="12.13671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -805,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>62</v>
@@ -823,10 +825,10 @@
         <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>67</v>
@@ -847,10 +849,10 @@
         <v>72</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>73</v>
@@ -868,10 +870,10 @@
         <v>77</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>78</v>
@@ -886,52 +888,52 @@
         <v>81</v>
       </c>
       <c r="AD1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AL1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AI1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="AP1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1076,7 +1078,7 @@
         <v>ناجح بتقدير مقبول</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1221,7 +1223,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1366,7 +1368,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1511,7 +1513,7 @@
         <v>ناجح ملحق</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1656,7 +1658,7 @@
         <v xml:space="preserve"> ناجح بتقدير متفوق </v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1801,7 +1803,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1946,7 +1948,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2024,7 +2026,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2169,7 +2171,7 @@
         <v>ناجح ملحق</v>
       </c>
     </row>
-    <row r="11" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2314,7 +2316,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2459,7 +2461,7 @@
         <v>ناجح بتقدير متميز</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2604,7 +2606,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2721,7 +2723,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2850,7 +2852,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2995,7 +2997,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3102,7 +3104,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="18" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3229,7 +3231,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3374,7 +3376,7 @@
         <v>ناجح بتقدير مقبول</v>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3519,7 +3521,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="21" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3662,7 +3664,7 @@
         <v>ناجح بتقدير مقبول</v>
       </c>
     </row>
-    <row r="22" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3807,7 +3809,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3952,7 +3954,7 @@
         <v>ناجح ملحق</v>
       </c>
     </row>
-    <row r="24" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4097,7 +4099,7 @@
         <v>ناجح ملحق</v>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4206,7 +4208,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="26" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4351,7 +4353,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="27" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4486,7 +4488,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="28" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4631,7 +4633,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="29" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -4776,7 +4778,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="30" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4921,7 +4923,7 @@
         <v>ناجح بتقدير متميز</v>
       </c>
     </row>
-    <row r="31" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5066,7 +5068,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="32" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5211,7 +5213,7 @@
         <v>ناجح بتقدير مقبول</v>
       </c>
     </row>
-    <row r="33" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5356,7 +5358,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="34" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5501,7 +5503,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="35" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5646,7 +5648,7 @@
         <v>ناجح بتقدير مقبول</v>
       </c>
     </row>
-    <row r="36" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5791,7 +5793,7 @@
         <v>ناجح ملحق</v>
       </c>
     </row>
-    <row r="37" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -5936,7 +5938,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="38" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -6081,7 +6083,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="39" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -6202,7 +6204,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="40" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -6333,7 +6335,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="41" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -6478,7 +6480,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="42" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -6623,7 +6625,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="43" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -6768,7 +6770,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="44" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -6913,7 +6915,7 @@
         <v>ناجح بتقدير مقبول</v>
       </c>
     </row>
-    <row r="45" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -7058,7 +7060,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="46" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -7203,7 +7205,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="47" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -7344,7 +7346,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="48" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -7489,7 +7491,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="49" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -7634,7 +7636,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="50" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -7779,7 +7781,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="51" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -7924,7 +7926,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="52" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -8069,7 +8071,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="53" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -8172,7 +8174,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="54" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -8317,7 +8319,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="55" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -8462,7 +8464,7 @@
         <v>ناجح بتقدير جيد</v>
       </c>
     </row>
-    <row r="56" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -8607,7 +8609,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="57" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -8734,7 +8736,7 @@
         <v xml:space="preserve"> ناجح بتقدير متفوق </v>
       </c>
     </row>
-    <row r="58" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -8879,7 +8881,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="59" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -8972,7 +8974,7 @@
         <v>راسب</v>
       </c>
     </row>
-    <row r="60" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:44" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -9072,7 +9074,7 @@
         <v>ناجح بتقدير متميز</v>
       </c>
     </row>
-    <row r="61" spans="1:44" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:44" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <conditionalFormatting sqref="C1">
     <cfRule type="top10" dxfId="1" priority="2" rank="3"/>
